--- a/www/ig/fhir/core/StructureDefinition-fr-core-patient.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5315" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5306" uniqueCount="690">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile of the Patient resource for France. This profile specifies the patient's identifiers for France. It uses international extensions (birtplace and nationality) and adds specific French extensions.
+    <t>Profile of the Patient resource for France. This profile specifies the patient's identifiers for France. It uses international extensions (birtplace and nationality) and adds specific French extensions.
 Ce profil spécifie les identifiants de patient utilisés en France. Il utilise des extensions internationales (birthplace et nationalité) et ajoute des extensions propres à la France.)</t>
   </si>
   <si>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Patient</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Patient|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -431,7 +431,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -444,14 +444,14 @@
     <t>Patient.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -473,6 +473,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0</t>
+  </si>
+  <si>
     <t>Patient.meta.security</t>
   </si>
   <si>
@@ -495,7 +498,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -519,7 +522,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -562,7 +565,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -638,11 +641,11 @@
     <t>nationality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-nationality}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-nationality|2.2.0}
 </t>
   </si>
   <si>
-    <t>Nationality</t>
+    <t>FR Core Nationality Extension</t>
   </si>
   <si>
     <t>The nationality of the patient.</t>
@@ -658,14 +661,16 @@
     <t>identityReliability</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability|2.2.0}
 </t>
   </si>
   <si>
     <t>Reliabilility of the identity | Fiabilité de l'identité</t>
   </si>
   <si>
-    <t>Reliabilility of the patient's identity | Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) avec la méthode de collection</t>
+    <t>Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) accompagné de la méthode de collection.
++Reliabilility of the patient's identity</t>
   </si>
   <si>
     <t>Patient.extension:deathPlace</t>
@@ -674,36 +679,41 @@
     <t>deathPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-death-place}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-death-place|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Patient Death Place Extension</t>
   </si>
   <si>
-    <t>Carries the death place of the patient |Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).</t>
-  </si>
-  <si>
-    <t>Patient.extension:birthdateUpdateIndicator</t>
-  </si>
-  <si>
-    <t>birthdateUpdateIndicator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator}
+    <t>Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).
++Carries the death place of the patient</t>
+  </si>
+  <si>
+    <t>Patient.extension:birthDateUpdateIndicator</t>
+  </si>
+  <si>
+    <t>birthDateUpdateIndicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Patient Birthdate Update Indicator Extension</t>
   </si>
   <si>
+    <t>Indicateur booléen de mise à jour de la date de naissance</t>
+  </si>
+  <si>
     <t>Patient.extension:birthPlace</t>
   </si>
   <si>
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace}
+    <t xml:space="preserve">Extension {patient-birthPlace|5.2.0}
 </t>
   </si>
   <si>
@@ -752,26 +762,21 @@
     <t>Patient.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
 </t>
   </si>
   <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
-  </si>
-  <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>XAD</t>
+    <t xml:space="preserve">ext-1
+</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -797,7 +802,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS validée, il est nécessaire de respecter la conformité au profil FrCorePatientINS. Les identifiants NIR et NIA ne sont définis uniquement dans le cas du FRCorePatientINS.</t>
+    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS au statut qualifié, il est nécessaire de respecter la conformité au profil FRCorePatientINS. Les identifiants NIR et NIA ne sont définis que dans le cas du FRCorePatientINS.</t>
   </si>
   <si>
     <t>An identifier for this patient.</t>
@@ -810,7 +815,7 @@
 </t>
   </si>
   <si>
-    <t>slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.)</t>
+    <t>Slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.)</t>
   </si>
   <si>
     <t>id</t>
@@ -880,7 +885,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-type|2.2.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -965,7 +970,7 @@
     <t>Patient.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1017,12 +1022,6 @@
     &lt;code value="NH"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:NSS.system</t>
@@ -1139,7 +1138,7 @@
     <t>PI</t>
   </si>
   <si>
-    <t>Hospital assigned patient identifier | IPP</t>
+    <t>Hospital assigned patient identifier | Identifiant Patient Permanent (IPP).</t>
   </si>
   <si>
     <t>Patient.identifier:PI.id</t>
@@ -1151,7 +1150,10 @@
     <t>Patient.identifier:PI.use</t>
   </si>
   <si>
-    <t>usual</t>
+    <t>La valeur old permet d'identifier des IPP désactivés (en cas de fusion d'identité pour résoudre des problèmes de doublonnage par exemple)</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-use-pi|2.2.0</t>
   </si>
   <si>
     <t>Patient.identifier:PI.type</t>
@@ -1254,7 +1256,7 @@
     <t>Patient.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0}
 </t>
   </si>
   <si>
@@ -1329,6 +1331,9 @@
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
   </si>
   <si>
+    <t>usual</t>
+  </si>
+  <si>
     <t>The use of a human name.</t>
   </si>
   <si>
@@ -1517,7 +1522,7 @@
     <t>birth-list-given-name</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birth-list-given-name}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birth-list-given-name|2.2.0}
 </t>
   </si>
   <si>
@@ -1551,14 +1556,14 @@
     <t>Patient.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
-    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
-  </si>
-  <si>
-    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
+    <t>A contact detail for the individual</t>
+  </si>
+  <si>
+    <t>A contact detail (e.g. a telephone number or an email address) by which the individual may be contacted.</t>
   </si>
   <si>
     <t>A Patient may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently and also to help with identification. The address might not go directly to the individual, but may reach another party that is able to proxy for the patient (i.e. home phone, or pet owner's phone).</t>
@@ -1567,23 +1572,22 @@
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>TEL</t>
-  </si>
-  <si>
-    <t>XTN</t>
+    <t>telecom</t>
+  </si>
+  <si>
+    <t>.telecom</t>
+  </si>
+  <si>
+    <t>PID-13, PID-14, PID-40</t>
   </si>
   <si>
     <t>Patient.gender</t>
   </si>
   <si>
-    <t>male | female | other | unknown</t>
-  </si>
-  <si>
-    <t>French patient's gender checked with the INSi teleservice | Genre du patient. Dans le cas d'une identité récupérée par le téléservice INSi, les valeurs sont M ou F</t>
+    <t>male | female | unknown</t>
+  </si>
+  <si>
+    <t>French patient's gender checked with the INSi teleservice | Genre administratif du patient. Dans le cas d'une identité récupérée par le téléservice INSi, les valeurs M ou F issues du téléservice sont à adapter à FHIR (male | female | unknown).</t>
   </si>
   <si>
     <t>The gender might not match the biological sex as determined by genetics or the individual's preferred identification. Note that for both humans and particularly animals, there are other legitimate possibilities than male and female, though the vast majority of systems and contexts only support male and female.  Systems providing decision support or enforcing business rules should ideally do this on the basis of Observations dealing with the specific sex or gender aspect of interest (anatomical, chromosomal, social, etc.)  However, because these observations are infrequently recorded, defaulting to the administrative gender is common practice.  Where such defaulting occurs, rule enforcement should allow for the variation between administrative and biological, chromosomal and other gender aspects.  For example, an alert about a hysterectomy on a male should be handled as a warning or overridable error, not a "hard" error.  See the Patient Gender and Sex section for additional information about communicating patient gender and sex.</t>
@@ -1592,10 +1596,7 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>The gender of a person used for administrative purposes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-gender|2.2.0</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>
@@ -1666,12 +1667,27 @@
     <t>Patient.address</t>
   </si>
   <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
+    <t>An address for the individual</t>
+  </si>
+  <si>
+    <t>An address for the individual.</t>
+  </si>
+  <si>
+    <t>Patient may have multiple addresses with different uses or applicable periods.</t>
   </si>
   <si>
     <t>May need to keep track of patient addresses for contacting, billing or reporting requirements and also to help with identification.</t>
   </si>
   <si>
+    <t>addr</t>
+  </si>
+  <si>
+    <t>.addr</t>
+  </si>
+  <si>
+    <t>PID-11</t>
+  </si>
+  <si>
     <t>Patient.maritalStatus</t>
   </si>
   <si>
@@ -1684,7 +1700,7 @@
     <t>Most, if not all systems capture it.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-marital-status</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-marital-status|2.2.0</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -1787,14 +1803,16 @@
     <t>contactIdentifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-identifier}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-identifier|2.2.0}
 </t>
   </si>
   <si>
-    <t>Contact identifier in the patient resource | Identifiant de contact dans la ressource Patient</t>
-  </si>
-  <si>
-    <t>This extension carries the contact identifier in the patient resource | Ajout d'un identifiant de contact dans la ressource Patient</t>
+    <t>FR Core Patient Contact Identifier Extension</t>
+  </si>
+  <si>
+    <t>Identifiant de contact dans la ressource Patient
++This extension carries the contact identifier in the patient resource</t>
   </si>
   <si>
     <t>Patient.contact.extension:comment</t>
@@ -1803,14 +1821,15 @@
     <t>comment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-comment}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-comment|2.2.0}
 </t>
   </si>
   <si>
-    <t>Comment on a dataElement | Commentaire sur un dataElement</t>
-  </si>
-  <si>
-    <t>add a comment on a dataElement  of a resource | Ajout d'un commentaire sur un dataElement d'une ressource</t>
+    <t>Comment on element Patient.contact | Commentaire sur l'élément Patient.contact</t>
+  </si>
+  <si>
+    <t>Ajout d'un commentaire sur un dataElement d'une ressource.
+Add a comment on a dataElement  of a resource</t>
   </si>
   <si>
     <t>Patient.contact.modifierExtension</t>
@@ -1845,11 +1864,7 @@
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:coding.system}
-</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
     <t>code</t>
@@ -1858,55 +1873,58 @@
     <t>NK1-7, NK1-3</t>
   </si>
   <si>
-    <t>Patient.contact.relationship:Role</t>
-  </si>
-  <si>
-    <t>Role</t>
+    <t>Patient.contact.relationship:role</t>
+  </si>
+  <si>
+    <t>role</t>
   </si>
   <si>
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelationType</t>
-  </si>
-  <si>
-    <t>RelationType</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.2.0</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:relationType</t>
+  </si>
+  <si>
+    <t>relationType</t>
   </si>
   <si>
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type|2.2.0</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
   </si>
   <si>
-    <t>Name of a human - parts and usage</t>
-  </si>
-  <si>
-    <t>A human's name with the ability to identify parts and usage.</t>
-  </si>
-  <si>
-    <t>Names may be changed, or repudiated, or people may have different names in different contexts. Names may be divided into parts of different type that have variable significance depending on context, though the division into parts does not always matter. With personal names, the different parts might or might not be imbued with some implicit meaning; various cultures associate different importance with the name parts and the degree to which systems must care about name parts around the world varies widely.</t>
+    <t>A name associated with the contact person</t>
+  </si>
+  <si>
+    <t>A name associated with the contact person.</t>
   </si>
   <si>
     <t>Contact persons need to be identified by name, but it is uncommon to need details about multiple other names for that contact person.</t>
   </si>
   <si>
-    <t>EN (actually, PN)</t>
-  </si>
-  <si>
-    <t>XPN</t>
+    <t>NK1-2</t>
   </si>
   <si>
     <t>Patient.contact.telecom</t>
   </si>
   <si>
+    <t>A contact detail for the person</t>
+  </si>
+  <si>
+    <t>A contact detail for the person, e.g. a telephone number or an email address.</t>
+  </si>
+  <si>
     <t>Contact may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
+  </si>
+  <si>
+    <t>NK1-5, NK1-6, NK1-40</t>
   </si>
   <si>
     <t>Patient.contact.address</t>
@@ -1925,19 +1943,25 @@
     <t>Need to keep track where the contact person can be contacted per postal mail or visited.</t>
   </si>
   <si>
-    <t>addr</t>
-  </si>
-  <si>
     <t>NK1-4</t>
   </si>
   <si>
     <t>Patient.contact.gender</t>
   </si>
   <si>
+    <t>male | female | other | unknown</t>
+  </si>
+  <si>
     <t>Administrative Gender - the gender that the contact person is considered to have for administration and record keeping purposes.</t>
   </si>
   <si>
     <t>Needed to address the person correctly.</t>
+  </si>
+  <si>
+    <t>The gender of a person used for administrative purposes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>NK1-15</t>
@@ -2062,7 +2086,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|PractitionerRole)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -2086,7 +2110,7 @@
     <t>Patient.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -2137,7 +2161,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -2478,17 +2502,17 @@
   <dimension ref="A1:AO142"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.3359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.95703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="20.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="147.0625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="140.6328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2497,27 +2521,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.3984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.5078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="73.109375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="33.4296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.98046875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="63.109375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="151.51171875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="39.390625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="54.296875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.4375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="130.69921875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="33.98046875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="46.8359375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.4296875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3742,7 +3766,7 @@
         <v>82</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>82</v>
@@ -3813,10 +3837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3839,16 +3863,16 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3874,13 +3898,13 @@
         <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>82</v>
@@ -3898,7 +3922,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3930,10 +3954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3956,16 +3980,16 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3991,13 +4015,13 @@
         <v>82</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>82</v>
@@ -4015,7 +4039,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -4047,10 +4071,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4076,13 +4100,13 @@
         <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4132,7 +4156,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4164,10 +4188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4190,16 +4214,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4225,13 +4249,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4249,7 +4273,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4281,14 +4305,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4307,16 +4331,16 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4366,7 +4390,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4381,7 +4405,7 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>82</v>
@@ -4398,14 +4422,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4424,16 +4448,16 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4483,7 +4507,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4498,7 +4522,7 @@
         <v>82</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -4515,10 +4539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4544,10 +4568,10 @@
         <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4596,7 +4620,7 @@
         <v>117</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4628,13 +4652,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>82</v>
@@ -4644,7 +4668,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
@@ -4656,13 +4680,13 @@
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4713,7 +4737,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4722,7 +4746,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>119</v>
@@ -4745,13 +4769,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>82</v>
@@ -4773,13 +4797,13 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4830,7 +4854,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4839,7 +4863,7 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>119</v>
@@ -4862,13 +4886,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4890,13 +4914,13 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4947,7 +4971,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4956,7 +4980,7 @@
         <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>119</v>
@@ -4979,13 +5003,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>82</v>
@@ -5007,13 +5031,13 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5064,7 +5088,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5073,7 +5097,7 @@
         <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>119</v>
@@ -5096,13 +5120,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>82</v>
@@ -5124,13 +5148,13 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5181,7 +5205,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5213,10 +5237,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5305,7 +5329,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>82</v>
@@ -5328,10 +5352,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5357,10 +5381,10 @@
         <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5443,10 +5467,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5472,13 +5496,13 @@
         <v>132</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5486,7 +5510,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5528,7 +5552,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5543,7 +5567,7 @@
         <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
@@ -5560,10 +5584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5586,17 +5610,15 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5645,7 +5667,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5654,13 +5676,13 @@
         <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5669,7 +5691,7 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5779,7 +5801,7 @@
         <v>119</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
@@ -6171,7 +6193,7 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>262</v>
@@ -6256,7 +6278,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6327,7 +6349,7 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
@@ -7211,7 +7233,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>90</v>
@@ -7226,7 +7248,7 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>262</v>
@@ -7311,7 +7333,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7382,13 +7404,11 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7438,7 +7458,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>280</v>
@@ -7449,7 +7469,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -7486,7 +7506,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>285</v>
@@ -7557,7 +7577,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>289</v>
@@ -7674,7 +7694,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>297</v>
@@ -7789,7 +7809,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>304</v>
@@ -7906,13 +7926,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>248</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>82</v>
@@ -7937,7 +7957,7 @@
         <v>249</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>251</v>
@@ -8025,7 +8045,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>259</v>
@@ -8140,7 +8160,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>260</v>
@@ -8257,7 +8277,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>261</v>
@@ -8268,7 +8288,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>90</v>
@@ -8283,7 +8303,7 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>262</v>
@@ -8305,7 +8325,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8368,7 +8388,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8376,7 +8396,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>271</v>
@@ -8408,7 +8428,7 @@
         <v>273</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>330</v>
+        <v>274</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>275</v>
@@ -8424,7 +8444,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8439,13 +8459,11 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8495,7 +8513,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>280</v>
@@ -8506,7 +8524,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>90</v>
@@ -8543,7 +8561,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>285</v>
@@ -8614,7 +8632,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>289</v>
@@ -8731,7 +8749,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>297</v>
@@ -8846,7 +8864,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>304</v>
@@ -8963,13 +8981,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>248</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>82</v>
@@ -8994,7 +9012,7 @@
         <v>249</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>251</v>
@@ -9082,7 +9100,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>259</v>
@@ -9197,7 +9215,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>260</v>
@@ -9314,7 +9332,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>261</v>
@@ -9325,7 +9343,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
@@ -9340,7 +9358,7 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>262</v>
@@ -9362,7 +9380,7 @@
         <v>82</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>82</v>
@@ -9425,7 +9443,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9433,7 +9451,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>271</v>
@@ -9481,7 +9499,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9496,13 +9514,11 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9552,7 +9568,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>280</v>
@@ -9600,7 +9616,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>285</v>
@@ -9671,7 +9687,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>289</v>
@@ -9788,7 +9804,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>297</v>
@@ -9903,7 +9919,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>304</v>
@@ -10020,13 +10036,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>248</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>82</v>
@@ -10051,7 +10067,7 @@
         <v>249</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>251</v>
@@ -10139,7 +10155,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>259</v>
@@ -10254,7 +10270,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>260</v>
@@ -10371,7 +10387,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>261</v>
@@ -10382,7 +10398,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>90</v>
@@ -10397,7 +10413,7 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>262</v>
@@ -10406,7 +10422,7 @@
         <v>263</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>264</v>
+        <v>359</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>265</v>
@@ -10419,7 +10435,7 @@
         <v>82</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>82</v>
@@ -10436,11 +10452,9 @@
       <c r="X68" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="Y68" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>268</v>
+        <v>360</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10482,7 +10496,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10490,7 +10504,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>271</v>
@@ -10538,7 +10552,7 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>82</v>
@@ -10553,13 +10567,11 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10609,7 +10621,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>280</v>
@@ -10728,7 +10740,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>289</v>
@@ -10845,7 +10857,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>297</v>
@@ -10960,7 +10972,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>304</v>
@@ -11077,13 +11089,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>248</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>82</v>
@@ -11108,7 +11120,7 @@
         <v>249</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>251</v>
@@ -11196,7 +11208,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>259</v>
@@ -11311,7 +11323,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>260</v>
@@ -11428,7 +11440,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>261</v>
@@ -11439,7 +11451,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>90</v>
@@ -11454,7 +11466,7 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>262</v>
@@ -11476,7 +11488,7 @@
         <v>82</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>82</v>
@@ -11539,7 +11551,7 @@
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11547,7 +11559,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>271</v>
@@ -11595,7 +11607,7 @@
         <v>82</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11610,13 +11622,11 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11666,7 +11676,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>280</v>
@@ -11785,7 +11795,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>289</v>
@@ -11902,7 +11912,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>297</v>
@@ -12017,7 +12027,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>304</v>
@@ -12134,10 +12144,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12160,26 +12170,26 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="O83" t="s" s="2">
+      <c r="P83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q83" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="P83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q83" t="s" s="2">
-        <v>386</v>
-      </c>
       <c r="R83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12223,7 +12233,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12238,13 +12248,13 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12255,10 +12265,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12281,19 +12291,19 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12330,7 +12340,7 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
@@ -12340,7 +12350,7 @@
         <v>117</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12355,16 +12365,16 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL84" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL84" t="s" s="2">
+      <c r="AM84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12372,13 +12382,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C85" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>82</v>
@@ -12400,19 +12410,19 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M85" t="s" s="2">
-        <v>403</v>
-      </c>
       <c r="N85" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O85" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12461,7 +12471,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12476,16 +12486,16 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL85" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL85" t="s" s="2">
+      <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12493,10 +12503,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12608,10 +12618,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12725,10 +12735,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12751,19 +12761,19 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12773,7 +12783,7 @@
         <v>82</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>361</v>
+        <v>413</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>82</v>
@@ -13547,7 +13557,7 @@
         <v>468</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>469</v>
@@ -13572,7 +13582,7 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>470</v>
@@ -13581,10 +13591,10 @@
         <v>471</v>
       </c>
       <c r="N95" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O95" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13633,7 +13643,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13648,16 +13658,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL95" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL95" t="s" s="2">
+      <c r="AM95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13668,7 +13678,7 @@
         <v>472</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13783,7 +13793,7 @@
         <v>473</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13900,7 +13910,7 @@
         <v>474</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>475</v>
@@ -14017,7 +14027,7 @@
         <v>479</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14040,19 +14050,19 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14856,7 +14866,7 @@
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>487</v>
@@ -14929,16 +14939,16 @@
         <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK106" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AK106" t="s" s="2">
+      <c r="AL106" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>82</v>
@@ -14978,7 +14988,7 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L107" t="s" s="2">
         <v>496</v>
@@ -15017,11 +15027,9 @@
       <c r="X107" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="Y107" t="s" s="2">
+      <c r="Y107" s="2"/>
+      <c r="Z107" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15054,16 +15062,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AL107" t="s" s="2">
+      <c r="AM107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15071,10 +15079,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15097,19 +15105,19 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15158,7 +15166,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15173,27 +15181,27 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AL108" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AL108" t="s" s="2">
+      <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
+      <c r="AO108" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>514</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15216,19 +15224,19 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15277,7 +15285,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15292,7 +15300,7 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>108</v>
@@ -15301,7 +15309,7 @@
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15309,10 +15317,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15332,22 +15340,22 @@
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>237</v>
+        <v>523</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>238</v>
+        <v>524</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15396,7 +15404,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15405,22 +15413,22 @@
         <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>241</v>
+        <v>527</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>242</v>
+        <v>529</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15428,10 +15436,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15457,14 +15465,14 @@
         <v>272</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15489,29 +15497,29 @@
         <v>82</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF111" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15526,16 +15534,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15543,10 +15551,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15569,19 +15577,19 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15630,7 +15638,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15645,7 +15653,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>108</v>
@@ -15654,7 +15662,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15662,10 +15670,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15688,19 +15696,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -15749,7 +15757,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15764,7 +15772,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>108</v>
@@ -15773,7 +15781,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15781,10 +15789,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15807,19 +15815,19 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -15868,7 +15876,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15880,10 +15888,10 @@
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>108</v>
@@ -15900,10 +15908,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16015,10 +16023,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16044,10 +16052,10 @@
         <v>111</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16128,13 +16136,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>82</v>
@@ -16156,13 +16164,13 @@
         <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16222,7 +16230,7 @@
         <v>81</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>119</v>
@@ -16245,13 +16253,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -16273,13 +16281,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16339,7 +16347,7 @@
         <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>119</v>
@@ -16362,14 +16370,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16391,10 +16399,10 @@
         <v>111</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>114</v>
@@ -16449,7 +16457,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16464,7 +16472,7 @@
         <v>119</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>82</v>
@@ -16481,10 +16489,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16510,14 +16518,14 @@
         <v>272</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16542,19 +16550,19 @@
         <v>82</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>581</v>
+        <v>142</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
@@ -16564,7 +16572,7 @@
         <v>117</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16579,7 +16587,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>108</v>
@@ -16588,7 +16596,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -16596,13 +16604,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>82</v>
@@ -16627,14 +16635,14 @@
         <v>272</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16659,11 +16667,11 @@
         <v>82</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16681,7 +16689,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16696,7 +16704,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16705,7 +16713,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16713,13 +16721,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16744,14 +16752,14 @@
         <v>272</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16776,11 +16784,11 @@
         <v>82</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16798,7 +16806,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16813,7 +16821,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16822,7 +16830,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16830,10 +16838,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16856,19 +16864,17 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16917,7 +16923,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16926,22 +16932,22 @@
         <v>90</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>597</v>
+        <v>395</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16949,10 +16955,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16978,13 +16984,13 @@
         <v>487</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>488</v>
+        <v>601</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>489</v>
+        <v>602</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>491</v>
@@ -17036,7 +17042,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17045,22 +17051,22 @@
         <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="AJ124" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK124" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AK124" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="AL124" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>494</v>
+        <v>604</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17068,10 +17074,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17094,17 +17100,17 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17153,7 +17159,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17168,7 +17174,7 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>606</v>
+        <v>527</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>108</v>
@@ -17177,7 +17183,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17185,10 +17191,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17211,17 +17217,17 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>496</v>
+        <v>612</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17249,10 +17255,10 @@
         <v>266</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>500</v>
+        <v>615</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>501</v>
+        <v>616</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>82</v>
@@ -17270,7 +17276,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17285,7 +17291,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
@@ -17294,7 +17300,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17302,10 +17308,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17331,14 +17337,14 @@
         <v>305</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17387,7 +17393,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17396,13 +17402,13 @@
         <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>108</v>
@@ -17411,7 +17417,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17419,10 +17425,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17448,10 +17454,10 @@
         <v>298</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17502,7 +17508,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17517,7 +17523,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>108</v>
@@ -17534,10 +17540,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17560,19 +17566,19 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -17621,7 +17627,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17636,10 +17642,10 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>82</v>
@@ -17653,10 +17659,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17768,10 +17774,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17885,14 +17891,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17914,10 +17920,10 @@
         <v>111</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>114</v>
@@ -17972,7 +17978,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -17987,7 +17993,7 @@
         <v>119</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>82</v>
@@ -18004,10 +18010,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18033,16 +18039,16 @@
         <v>272</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18067,13 +18073,13 @@
         <v>82</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>82</v>
@@ -18091,7 +18097,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>90</v>
@@ -18106,16 +18112,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18123,10 +18129,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18149,19 +18155,19 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18210,7 +18216,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18225,16 +18231,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18242,14 +18248,14 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18268,16 +18274,16 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18327,7 +18333,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18342,7 +18348,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>108</v>
@@ -18351,7 +18357,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18359,10 +18365,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18385,19 +18391,19 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18446,7 +18452,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18461,10 +18467,10 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>82</v>
@@ -18478,10 +18484,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18504,19 +18510,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18565,7 +18571,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18580,7 +18586,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>108</v>
@@ -18597,10 +18603,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18712,10 +18718,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18829,14 +18835,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18858,10 +18864,10 @@
         <v>111</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>114</v>
@@ -18916,7 +18922,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -18931,7 +18937,7 @@
         <v>119</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>82</v>
@@ -18948,10 +18954,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18974,16 +18980,16 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19033,7 +19039,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>90</v>
@@ -19057,7 +19063,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19065,10 +19071,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19091,13 +19097,13 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19127,10 +19133,10 @@
         <v>266</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19148,7 +19154,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -19163,7 +19169,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>108</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-patient.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5306" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5315" uniqueCount="684">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile of the Patient resource for France. This profile specifies the patient's identifiers for France. It uses international extensions (birtplace and nationality) and adds specific French extensions.
+    <t>Profile of the Patient resource for France. This profile specifies the patient's identifiers for France. It uses international extensions (birtplace and nationality) and adds specific French extensions.
 Ce profil spécifie les identifiants de patient utilisés en France. Il utilise des extensions internationales (birthplace et nationalité) et ajoute des extensions propres à la France.)</t>
   </si>
   <si>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Patient|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Patient</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -431,7 +431,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -444,14 +444,14 @@
     <t>Patient.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -473,9 +473,6 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0</t>
-  </si>
-  <si>
     <t>Patient.meta.security</t>
   </si>
   <si>
@@ -498,7 +495,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -522,7 +519,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -565,7 +562,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -641,11 +638,11 @@
     <t>nationality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-nationality|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-nationality}
 </t>
   </si>
   <si>
-    <t>FR Core Nationality Extension</t>
+    <t>Nationality</t>
   </si>
   <si>
     <t>The nationality of the patient.</t>
@@ -661,16 +658,14 @@
     <t>identityReliability</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability}
 </t>
   </si>
   <si>
     <t>Reliabilility of the identity | Fiabilité de l'identité</t>
   </si>
   <si>
-    <t>Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) accompagné de la méthode de collection.
--Reliabilility of the patient's identity</t>
+    <t>Reliabilility of the patient's identity | Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) avec la méthode de collection</t>
   </si>
   <si>
     <t>Patient.extension:deathPlace</t>
@@ -679,41 +674,36 @@
     <t>deathPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-death-place|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-death-place}
 </t>
   </si>
   <si>
     <t>FR Core Patient Death Place Extension</t>
   </si>
   <si>
-    <t>Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).
--Carries the death place of the patient</t>
-  </si>
-  <si>
-    <t>Patient.extension:birthDateUpdateIndicator</t>
-  </si>
-  <si>
-    <t>birthDateUpdateIndicator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator|2.2.0}
+    <t>Carries the death place of the patient |Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).</t>
+  </si>
+  <si>
+    <t>Patient.extension:birthdateUpdateIndicator</t>
+  </si>
+  <si>
+    <t>birthdateUpdateIndicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator}
 </t>
   </si>
   <si>
     <t>FR Core Patient Birthdate Update Indicator Extension</t>
   </si>
   <si>
-    <t>Indicateur booléen de mise à jour de la date de naissance</t>
-  </si>
-  <si>
     <t>Patient.extension:birthPlace</t>
   </si>
   <si>
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace|5.2.0}
+    <t xml:space="preserve">Extension {patient-birthPlace}
 </t>
   </si>
   <si>
@@ -762,21 +752,26 @@
     <t>Patient.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
+  </si>
+  <si>
+    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
+  </si>
+  <si>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ext-1
-</t>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>XAD</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -802,7 +797,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS au statut qualifié, il est nécessaire de respecter la conformité au profil FRCorePatientINS. Les identifiants NIR et NIA ne sont définis que dans le cas du FRCorePatientINS.</t>
+    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS validée, il est nécessaire de respecter la conformité au profil FrCorePatientINS. Les identifiants NIR et NIA ne sont définis uniquement dans le cas du FRCorePatientINS.</t>
   </si>
   <si>
     <t>An identifier for this patient.</t>
@@ -815,7 +810,7 @@
 </t>
   </si>
   <si>
-    <t>Slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.)</t>
+    <t>slicing de l'identifiant Patient sur le type d'identifiant (IPP, INS-NIR, INS-NIA, etc.)</t>
   </si>
   <si>
     <t>id</t>
@@ -885,7 +880,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-type|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -970,7 +965,7 @@
     <t>Patient.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1022,6 +1017,12 @@
     &lt;code value="NH"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:NSS.system</t>
@@ -1138,7 +1139,7 @@
     <t>PI</t>
   </si>
   <si>
-    <t>Hospital assigned patient identifier | Identifiant Patient Permanent (IPP).</t>
+    <t>Hospital assigned patient identifier | IPP</t>
   </si>
   <si>
     <t>Patient.identifier:PI.id</t>
@@ -1150,10 +1151,7 @@
     <t>Patient.identifier:PI.use</t>
   </si>
   <si>
-    <t>La valeur old permet d'identifier des IPP désactivés (en cas de fusion d'identité pour résoudre des problèmes de doublonnage par exemple)</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-use-pi|2.2.0</t>
+    <t>usual</t>
   </si>
   <si>
     <t>Patient.identifier:PI.type</t>
@@ -1256,7 +1254,7 @@
     <t>Patient.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
 </t>
   </si>
   <si>
@@ -1331,9 +1329,6 @@
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
   </si>
   <si>
-    <t>usual</t>
-  </si>
-  <si>
     <t>The use of a human name.</t>
   </si>
   <si>
@@ -1522,7 +1517,7 @@
     <t>birth-list-given-name</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birth-list-given-name|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birth-list-given-name}
 </t>
   </si>
   <si>
@@ -1556,14 +1551,14 @@
     <t>Patient.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
-    <t>A contact detail for the individual</t>
-  </si>
-  <si>
-    <t>A contact detail (e.g. a telephone number or an email address) by which the individual may be contacted.</t>
+    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
+  </si>
+  <si>
+    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
   </si>
   <si>
     <t>A Patient may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently and also to help with identification. The address might not go directly to the individual, but may reach another party that is able to proxy for the patient (i.e. home phone, or pet owner's phone).</t>
@@ -1572,22 +1567,23 @@
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
-    <t>telecom</t>
-  </si>
-  <si>
-    <t>.telecom</t>
-  </si>
-  <si>
-    <t>PID-13, PID-14, PID-40</t>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>TEL</t>
+  </si>
+  <si>
+    <t>XTN</t>
   </si>
   <si>
     <t>Patient.gender</t>
   </si>
   <si>
-    <t>male | female | unknown</t>
-  </si>
-  <si>
-    <t>French patient's gender checked with the INSi teleservice | Genre administratif du patient. Dans le cas d'une identité récupérée par le téléservice INSi, les valeurs M ou F issues du téléservice sont à adapter à FHIR (male | female | unknown).</t>
+    <t>male | female | other | unknown</t>
+  </si>
+  <si>
+    <t>French patient's gender checked with the INSi teleservice | Genre du patient. Dans le cas d'une identité récupérée par le téléservice INSi, les valeurs sont M ou F</t>
   </si>
   <si>
     <t>The gender might not match the biological sex as determined by genetics or the individual's preferred identification. Note that for both humans and particularly animals, there are other legitimate possibilities than male and female, though the vast majority of systems and contexts only support male and female.  Systems providing decision support or enforcing business rules should ideally do this on the basis of Observations dealing with the specific sex or gender aspect of interest (anatomical, chromosomal, social, etc.)  However, because these observations are infrequently recorded, defaulting to the administrative gender is common practice.  Where such defaulting occurs, rule enforcement should allow for the variation between administrative and biological, chromosomal and other gender aspects.  For example, an alert about a hysterectomy on a male should be handled as a warning or overridable error, not a "hard" error.  See the Patient Gender and Sex section for additional information about communicating patient gender and sex.</t>
@@ -1596,7 +1592,10 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-gender|2.2.0</t>
+    <t>The gender of a person used for administrative purposes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>
@@ -1667,27 +1666,12 @@
     <t>Patient.address</t>
   </si>
   <si>
-    <t>An address for the individual</t>
-  </si>
-  <si>
-    <t>An address for the individual.</t>
-  </si>
-  <si>
-    <t>Patient may have multiple addresses with different uses or applicable periods.</t>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>May need to keep track of patient addresses for contacting, billing or reporting requirements and also to help with identification.</t>
   </si>
   <si>
-    <t>addr</t>
-  </si>
-  <si>
-    <t>.addr</t>
-  </si>
-  <si>
-    <t>PID-11</t>
-  </si>
-  <si>
     <t>Patient.maritalStatus</t>
   </si>
   <si>
@@ -1700,7 +1684,7 @@
     <t>Most, if not all systems capture it.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-marital-status|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-marital-status</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -1803,16 +1787,14 @@
     <t>contactIdentifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-identifier|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-identifier}
 </t>
   </si>
   <si>
-    <t>FR Core Patient Contact Identifier Extension</t>
-  </si>
-  <si>
-    <t>Identifiant de contact dans la ressource Patient
--This extension carries the contact identifier in the patient resource</t>
+    <t>Contact identifier in the patient resource | Identifiant de contact dans la ressource Patient</t>
+  </si>
+  <si>
+    <t>This extension carries the contact identifier in the patient resource | Ajout d'un identifiant de contact dans la ressource Patient</t>
   </si>
   <si>
     <t>Patient.contact.extension:comment</t>
@@ -1821,15 +1803,14 @@
     <t>comment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-comment|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-comment}
 </t>
   </si>
   <si>
-    <t>Comment on element Patient.contact | Commentaire sur l'élément Patient.contact</t>
-  </si>
-  <si>
-    <t>Ajout d'un commentaire sur un dataElement d'une ressource.
-Add a comment on a dataElement  of a resource</t>
+    <t>Comment on a dataElement | Commentaire sur un dataElement</t>
+  </si>
+  <si>
+    <t>add a comment on a dataElement  of a resource | Ajout d'un commentaire sur un dataElement d'une ressource</t>
   </si>
   <si>
     <t>Patient.contact.modifierExtension</t>
@@ -1864,7 +1845,11 @@
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.system}
+</t>
   </si>
   <si>
     <t>code</t>
@@ -1873,58 +1858,55 @@
     <t>NK1-7, NK1-3</t>
   </si>
   <si>
-    <t>Patient.contact.relationship:role</t>
-  </si>
-  <si>
-    <t>role</t>
+    <t>Patient.contact.relationship:Role</t>
+  </si>
+  <si>
+    <t>Role</t>
   </si>
   <si>
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.2.0</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:relationType</t>
-  </si>
-  <si>
-    <t>relationType</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:RelationType</t>
+  </si>
+  <si>
+    <t>RelationType</t>
   </si>
   <si>
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
   </si>
   <si>
-    <t>A name associated with the contact person</t>
-  </si>
-  <si>
-    <t>A name associated with the contact person.</t>
+    <t>Name of a human - parts and usage</t>
+  </si>
+  <si>
+    <t>A human's name with the ability to identify parts and usage.</t>
+  </si>
+  <si>
+    <t>Names may be changed, or repudiated, or people may have different names in different contexts. Names may be divided into parts of different type that have variable significance depending on context, though the division into parts does not always matter. With personal names, the different parts might or might not be imbued with some implicit meaning; various cultures associate different importance with the name parts and the degree to which systems must care about name parts around the world varies widely.</t>
   </si>
   <si>
     <t>Contact persons need to be identified by name, but it is uncommon to need details about multiple other names for that contact person.</t>
   </si>
   <si>
-    <t>NK1-2</t>
+    <t>EN (actually, PN)</t>
+  </si>
+  <si>
+    <t>XPN</t>
   </si>
   <si>
     <t>Patient.contact.telecom</t>
   </si>
   <si>
-    <t>A contact detail for the person</t>
-  </si>
-  <si>
-    <t>A contact detail for the person, e.g. a telephone number or an email address.</t>
-  </si>
-  <si>
     <t>Contact may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
-  </si>
-  <si>
-    <t>NK1-5, NK1-6, NK1-40</t>
   </si>
   <si>
     <t>Patient.contact.address</t>
@@ -1943,25 +1925,19 @@
     <t>Need to keep track where the contact person can be contacted per postal mail or visited.</t>
   </si>
   <si>
+    <t>addr</t>
+  </si>
+  <si>
     <t>NK1-4</t>
   </si>
   <si>
     <t>Patient.contact.gender</t>
   </si>
   <si>
-    <t>male | female | other | unknown</t>
-  </si>
-  <si>
     <t>Administrative Gender - the gender that the contact person is considered to have for administration and record keeping purposes.</t>
   </si>
   <si>
     <t>Needed to address the person correctly.</t>
-  </si>
-  <si>
-    <t>The gender of a person used for administrative purposes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>NK1-15</t>
@@ -2086,7 +2062,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|PractitionerRole)
 </t>
   </si>
   <si>
@@ -2110,7 +2086,7 @@
     <t>Patient.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2161,7 +2137,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -2502,17 +2478,17 @@
   <dimension ref="A1:AO142"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.5390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.95703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="53.953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.203125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.3359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="140.6328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="147.0625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2521,27 +2497,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.98046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="63.109375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.3984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.5078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="73.109375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="33.4296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="130.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="33.98046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="46.8359375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.4296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="151.51171875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.390625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="54.296875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="36.4375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3766,7 +3742,7 @@
         <v>82</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>147</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>82</v>
@@ -3837,10 +3813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3863,16 +3839,16 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3898,31 +3874,31 @@
         <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3954,10 +3930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3980,16 +3956,16 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4015,31 +3991,31 @@
         <v>82</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -4071,10 +4047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4100,13 +4076,13 @@
         <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4156,7 +4132,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4188,10 +4164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4214,16 +4190,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4249,31 +4225,31 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4305,14 +4281,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4331,16 +4307,16 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4390,7 +4366,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4405,7 +4381,7 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>82</v>
@@ -4422,14 +4398,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4448,16 +4424,16 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4507,7 +4483,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4522,7 +4498,7 @@
         <v>82</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -4539,10 +4515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4568,10 +4544,10 @@
         <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4620,7 +4596,7 @@
         <v>117</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4652,13 +4628,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>82</v>
@@ -4668,7 +4644,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
@@ -4680,13 +4656,13 @@
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4737,7 +4713,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4746,7 +4722,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>119</v>
@@ -4769,13 +4745,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>82</v>
@@ -4797,13 +4773,13 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4854,7 +4830,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4863,7 +4839,7 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>119</v>
@@ -4886,13 +4862,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4914,13 +4890,13 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4971,7 +4947,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4980,7 +4956,7 @@
         <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>119</v>
@@ -5003,13 +4979,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>82</v>
@@ -5031,13 +5007,13 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>218</v>
-      </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5088,7 +5064,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5097,7 +5073,7 @@
         <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>119</v>
@@ -5120,13 +5096,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>82</v>
@@ -5148,13 +5124,13 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5205,7 +5181,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5237,10 +5213,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5329,7 +5305,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>82</v>
@@ -5352,10 +5328,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5381,10 +5357,10 @@
         <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5467,10 +5443,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5496,13 +5472,13 @@
         <v>132</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5510,7 +5486,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5552,7 +5528,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5567,7 +5543,7 @@
         <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
@@ -5584,10 +5560,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5610,15 +5586,17 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5667,7 +5645,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5676,13 +5654,13 @@
         <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5691,7 +5669,7 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5801,7 +5779,7 @@
         <v>119</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
@@ -6193,7 +6171,7 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>262</v>
@@ -6278,7 +6256,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6349,7 +6327,7 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
@@ -7233,7 +7211,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>90</v>
@@ -7248,7 +7226,7 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>262</v>
@@ -7333,7 +7311,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7404,11 +7382,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7458,7 +7438,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>280</v>
@@ -7469,7 +7449,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -7506,7 +7486,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>285</v>
@@ -7577,7 +7557,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>289</v>
@@ -7694,7 +7674,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>297</v>
@@ -7809,7 +7789,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>304</v>
@@ -7926,13 +7906,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>248</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>82</v>
@@ -7957,7 +7937,7 @@
         <v>249</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>251</v>
@@ -8045,7 +8025,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>259</v>
@@ -8160,7 +8140,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>260</v>
@@ -8277,7 +8257,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>261</v>
@@ -8288,7 +8268,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>90</v>
@@ -8303,7 +8283,7 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>262</v>
@@ -8325,7 +8305,7 @@
         <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>82</v>
@@ -8388,7 +8368,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8396,7 +8376,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>271</v>
@@ -8428,7 +8408,7 @@
         <v>273</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>274</v>
+        <v>330</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>275</v>
@@ -8444,7 +8424,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8459,11 +8439,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8513,7 +8495,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>280</v>
@@ -8524,7 +8506,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>90</v>
@@ -8561,7 +8543,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>285</v>
@@ -8632,7 +8614,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>289</v>
@@ -8749,7 +8731,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>297</v>
@@ -8864,7 +8846,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>304</v>
@@ -8981,13 +8963,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>248</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>82</v>
@@ -9012,7 +8994,7 @@
         <v>249</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>251</v>
@@ -9100,7 +9082,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>259</v>
@@ -9215,7 +9197,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>260</v>
@@ -9332,7 +9314,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>261</v>
@@ -9343,7 +9325,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
@@ -9358,7 +9340,7 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>262</v>
@@ -9380,7 +9362,7 @@
         <v>82</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>82</v>
@@ -9443,7 +9425,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9451,7 +9433,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>271</v>
@@ -9499,7 +9481,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9514,11 +9496,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9568,7 +9552,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>280</v>
@@ -9616,7 +9600,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>285</v>
@@ -9687,7 +9671,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>289</v>
@@ -9804,7 +9788,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>297</v>
@@ -9919,7 +9903,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>304</v>
@@ -10036,13 +10020,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>248</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>82</v>
@@ -10067,7 +10051,7 @@
         <v>249</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>251</v>
@@ -10155,7 +10139,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>259</v>
@@ -10270,7 +10254,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>260</v>
@@ -10387,7 +10371,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>261</v>
@@ -10398,7 +10382,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>90</v>
@@ -10413,7 +10397,7 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>262</v>
@@ -10422,7 +10406,7 @@
         <v>263</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>359</v>
+        <v>264</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>265</v>
@@ -10435,7 +10419,7 @@
         <v>82</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>82</v>
@@ -10452,9 +10436,11 @@
       <c r="X68" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="Y68" s="2"/>
+      <c r="Y68" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>360</v>
+        <v>268</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10496,7 +10482,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10504,7 +10490,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>271</v>
@@ -10552,7 +10538,7 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>82</v>
@@ -10567,11 +10553,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10621,7 +10609,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>280</v>
@@ -10740,7 +10728,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>289</v>
@@ -10857,7 +10845,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>297</v>
@@ -10972,7 +10960,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>304</v>
@@ -11089,13 +11077,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>248</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>82</v>
@@ -11120,7 +11108,7 @@
         <v>249</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>251</v>
@@ -11208,7 +11196,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>259</v>
@@ -11323,7 +11311,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>260</v>
@@ -11440,7 +11428,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>261</v>
@@ -11451,7 +11439,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>90</v>
@@ -11466,7 +11454,7 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>262</v>
@@ -11488,7 +11476,7 @@
         <v>82</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>82</v>
@@ -11551,7 +11539,7 @@
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11559,7 +11547,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>271</v>
@@ -11607,7 +11595,7 @@
         <v>82</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11622,11 +11610,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11676,7 +11666,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>280</v>
@@ -11795,7 +11785,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>289</v>
@@ -11912,7 +11902,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>297</v>
@@ -12027,7 +12017,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>304</v>
@@ -12144,10 +12134,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12170,70 +12160,70 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q83" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="R83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q83" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="R83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12248,13 +12238,13 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12265,10 +12255,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12291,19 +12281,19 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12340,7 +12330,7 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
@@ -12350,7 +12340,7 @@
         <v>117</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12365,16 +12355,16 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12382,13 +12372,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>82</v>
@@ -12410,19 +12400,19 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12471,7 +12461,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12486,16 +12476,16 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12503,10 +12493,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12618,10 +12608,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12735,10 +12725,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12761,19 +12751,19 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12783,7 +12773,7 @@
         <v>82</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>413</v>
+        <v>361</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>82</v>
@@ -13557,7 +13547,7 @@
         <v>468</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>469</v>
@@ -13582,7 +13572,7 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>470</v>
@@ -13591,10 +13581,10 @@
         <v>471</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13643,7 +13633,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13658,16 +13648,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13678,7 +13668,7 @@
         <v>472</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13793,7 +13783,7 @@
         <v>473</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13910,7 +13900,7 @@
         <v>474</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>475</v>
@@ -14027,7 +14017,7 @@
         <v>479</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14050,19 +14040,19 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14866,7 +14856,7 @@
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>487</v>
@@ -14939,16 +14929,16 @@
         <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>102</v>
+        <v>492</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>82</v>
@@ -14988,7 +14978,7 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L107" t="s" s="2">
         <v>496</v>
@@ -15027,9 +15017,11 @@
       <c r="X107" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="Y107" s="2"/>
+      <c r="Y107" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15062,16 +15054,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15079,10 +15071,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15105,19 +15097,19 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15166,7 +15158,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15181,27 +15173,27 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15224,19 +15216,19 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15285,7 +15277,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15300,7 +15292,7 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>108</v>
@@ -15309,7 +15301,7 @@
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15317,10 +15309,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15340,22 +15332,22 @@
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L110" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15404,7 +15396,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15413,22 +15405,22 @@
         <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>527</v>
+        <v>241</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>529</v>
+        <v>242</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15436,10 +15428,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15465,14 +15457,14 @@
         <v>272</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15497,11 +15489,11 @@
         <v>82</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15519,7 +15511,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15534,16 +15526,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15551,10 +15543,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15577,19 +15569,19 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O112" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15638,7 +15630,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15653,7 +15645,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>108</v>
@@ -15662,7 +15654,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15670,10 +15662,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15696,19 +15688,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="O113" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -15757,7 +15749,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15772,7 +15764,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>108</v>
@@ -15781,7 +15773,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15789,10 +15781,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15815,19 +15807,19 @@
         <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="O114" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -15876,7 +15868,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15888,10 +15880,10 @@
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>108</v>
@@ -15908,10 +15900,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16023,10 +16015,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16052,10 +16044,10 @@
         <v>111</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16136,13 +16128,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>82</v>
@@ -16164,13 +16156,13 @@
         <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16230,7 +16222,7 @@
         <v>81</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>119</v>
@@ -16253,13 +16245,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
@@ -16281,13 +16273,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16347,7 +16339,7 @@
         <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>119</v>
@@ -16370,14 +16362,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16399,10 +16391,10 @@
         <v>111</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>114</v>
@@ -16457,7 +16449,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16472,7 +16464,7 @@
         <v>119</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>82</v>
@@ -16489,10 +16481,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16518,14 +16510,14 @@
         <v>272</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16550,19 +16542,19 @@
         <v>82</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>142</v>
+        <v>581</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
@@ -16572,7 +16564,7 @@
         <v>117</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16587,7 +16579,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>108</v>
@@ -16596,7 +16588,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -16604,13 +16596,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>82</v>
@@ -16635,14 +16627,14 @@
         <v>272</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16667,11 +16659,11 @@
         <v>82</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16689,7 +16681,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16704,7 +16696,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>108</v>
@@ -16713,7 +16705,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16721,13 +16713,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>82</v>
@@ -16752,14 +16744,14 @@
         <v>272</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16784,11 +16776,11 @@
         <v>82</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16806,7 +16798,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16821,7 +16813,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16830,7 +16822,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16838,10 +16830,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16864,17 +16856,19 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O123" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16923,7 +16917,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16932,22 +16926,22 @@
         <v>90</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>395</v>
+        <v>597</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16955,10 +16949,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16984,13 +16978,13 @@
         <v>487</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>601</v>
+        <v>488</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>602</v>
+        <v>489</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>491</v>
@@ -17042,7 +17036,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17051,22 +17045,22 @@
         <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>102</v>
+        <v>492</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>604</v>
+        <v>494</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17074,10 +17068,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17100,17 +17094,17 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17159,7 +17153,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17174,7 +17168,7 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>527</v>
+        <v>606</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>108</v>
@@ -17183,7 +17177,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17191,10 +17185,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17217,17 +17211,17 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>612</v>
+        <v>496</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17255,10 +17249,10 @@
         <v>266</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>615</v>
+        <v>500</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>616</v>
+        <v>501</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>82</v>
@@ -17276,7 +17270,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17291,7 +17285,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>108</v>
@@ -17300,7 +17294,7 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17308,10 +17302,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17337,14 +17331,14 @@
         <v>305</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17393,7 +17387,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17402,13 +17396,13 @@
         <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>108</v>
@@ -17417,7 +17411,7 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17425,10 +17419,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17454,10 +17448,10 @@
         <v>298</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17508,7 +17502,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17523,7 +17517,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>108</v>
@@ -17540,10 +17534,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17566,19 +17560,19 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -17627,7 +17621,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17642,10 +17636,10 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>82</v>
@@ -17659,10 +17653,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17774,10 +17768,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17891,14 +17885,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17920,10 +17914,10 @@
         <v>111</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>114</v>
@@ -17978,7 +17972,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -17993,7 +17987,7 @@
         <v>119</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>82</v>
@@ -18010,10 +18004,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18039,16 +18033,16 @@
         <v>272</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18073,14 +18067,14 @@
         <v>82</v>
       </c>
       <c r="X133" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y133" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y133" t="s" s="2">
+      <c r="Z133" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Z133" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="AA133" t="s" s="2">
         <v>82</v>
       </c>
@@ -18097,7 +18091,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>90</v>
@@ -18112,16 +18106,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18129,10 +18123,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18155,19 +18149,19 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18216,7 +18210,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18231,16 +18225,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18248,14 +18242,14 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18274,16 +18268,16 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18333,7 +18327,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18348,7 +18342,7 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>108</v>
@@ -18357,7 +18351,7 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18365,10 +18359,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18391,19 +18385,19 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18452,7 +18446,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18467,10 +18461,10 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>82</v>
@@ -18484,10 +18478,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18510,19 +18504,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18571,7 +18565,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18586,7 +18580,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>108</v>
@@ -18603,10 +18597,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18718,10 +18712,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18835,14 +18829,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18864,10 +18858,10 @@
         <v>111</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>114</v>
@@ -18922,7 +18916,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -18937,7 +18931,7 @@
         <v>119</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>82</v>
@@ -18954,10 +18948,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18980,16 +18974,16 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19039,7 +19033,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>90</v>
@@ -19063,7 +19057,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19071,10 +19065,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19097,13 +19091,13 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19133,10 +19127,10 @@
         <v>266</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19154,7 +19148,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>90</v>
@@ -19169,7 +19163,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>108</v>
